--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_80/per_file_predictions_epoch_80.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_80/per_file_predictions_epoch_80.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="501">
   <si>
     <t>Filename</t>
   </si>
@@ -808,682 +808,715 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9825,0.0088,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9374,0.0003,0.0006,0.0474</t>
-  </si>
-  <si>
-    <t>0.8450,0.0002,0.0001,0.1441</t>
+    <t>0.9873,0.0035,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9863,0.0001,0.0000,0.0134</t>
+  </si>
+  <si>
+    <t>0.3978,0.0002,0.0000,0.7817</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0015,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9917,0.0010,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0010,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0600,0.0002,0.9688,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9985,0.0004</t>
-  </si>
-  <si>
-    <t>0.9942,0.0010,0.0016,0.0001</t>
+    <t>0.9345,0.0005,0.0753,0.0001</t>
+  </si>
+  <si>
+    <t>0.5245,0.0026,0.5002,0.0002</t>
+  </si>
+  <si>
+    <t>0.1733,0.0003,0.9430,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.9617,0.0029,0.0281,0.0002</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9978,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0001</t>
+    <t>0.0009,0.9984,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.9959,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0160,0.0001,0.9775,0.0014</t>
+  </si>
+  <si>
+    <t>0.0125,0.0068,0.9764,0.0011</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.0003,0.9938,0.0006</t>
+  </si>
+  <si>
+    <t>0.0526,0.0002,0.9677,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.2540,0.7962,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.2348,0.1346,0.4545,0.0011</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9995,0.0045</t>
+  </si>
+  <si>
+    <t>0.0012,0.9858,0.0592,0.0005</t>
+  </si>
+  <si>
+    <t>0.9740,0.0260,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.7957,0.0095,0.0944,0.0016</t>
+  </si>
+  <si>
+    <t>0.7228,0.3537,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.9908,0.0119,0.0005</t>
+  </si>
+  <si>
+    <t>0.0027,0.0203,0.9716,0.0031</t>
+  </si>
+  <si>
+    <t>0.0018,0.0032,0.9929,0.0019</t>
+  </si>
+  <si>
+    <t>0.0007,0.0020,0.9975,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0188,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9988,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.0010,0.9969,0.0005</t>
+  </si>
+  <si>
+    <t>0.0119,0.8555,0.0008,0.5263</t>
+  </si>
+  <si>
+    <t>0.0003,0.9970,0.0041,0.0085</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0225,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0692,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0006,0.9979,0.0006</t>
+  </si>
+  <si>
+    <t>0.9806,0.0236,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9995,0.0051</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0055,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9920,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0007,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9981,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9824,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9800,0.0003,0.0298,0.0000</t>
+  </si>
+  <si>
+    <t>0.3573,0.0004,0.7649,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9998,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9685,0.9895,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9883,0.9252,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.1310,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.9372,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0010,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.0018,0.9990</t>
+  </si>
+  <si>
+    <t>0.0002,0.0005,0.0002,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.6502,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9921,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9078,0.9460,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0189,0.9959,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9936,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9910,0.4543,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0018,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9956,0.0039,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9993,0.0009</t>
+  </si>
+  <si>
+    <t>0.0005,0.0004,0.9990,0.0001</t>
+  </si>
+  <si>
+    <t>0.9510,0.0003,0.0241,0.0010</t>
+  </si>
+  <si>
+    <t>0.0006,0.0001,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9986,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.5387,0.0003,0.4582,0.0021</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9992,0.0002</t>
-  </si>
-  <si>
-    <t>0.0290,0.0000,0.9853,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0006,0.9884,0.0009</t>
-  </si>
-  <si>
-    <t>0.0143,0.0001,0.9921,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0170,0.9754,0.0034,0.0027</t>
-  </si>
-  <si>
-    <t>0.3222,0.0217,0.5757,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0081,0.9982,0.0068</t>
-  </si>
-  <si>
-    <t>0.0022,0.5596,0.8020,0.0011</t>
-  </si>
-  <si>
-    <t>0.9771,0.0152,0.0043,0.0013</t>
-  </si>
-  <si>
-    <t>0.7339,0.0090,0.1363,0.0037</t>
-  </si>
-  <si>
-    <t>0.6764,0.3983,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9982,0.0083,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.1694,0.8438,0.0030</t>
-  </si>
-  <si>
-    <t>0.0020,0.0016,0.9826,0.0191</t>
-  </si>
-  <si>
-    <t>0.0041,0.0012,0.9909,0.0006</t>
-  </si>
-  <si>
-    <t>0.1110,0.0003,0.9137,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0293,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9960,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.7280,0.0005,0.9903</t>
-  </si>
-  <si>
-    <t>0.0016,0.9936,0.0030,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0025,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0747,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0023,0.9976,0.0005</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0004,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9919,0.0011,0.0051,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9996,0.0058</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0016,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0028,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9801,0.9782,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0442,0.9964,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.7773,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8471,0.0002,0.3008,0.0001</t>
-  </si>
-  <si>
-    <t>0.1688,0.0012,0.8817,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9994,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9900,0.9873,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9743,0.9947,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.0722,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.9815,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.0008,0.9992</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0008,0.9993</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.0010,0.9996</t>
+    <t>0.0169,0.9861,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.8960,0.0406,0.0157,0.0007</t>
+  </si>
+  <si>
+    <t>0.9847,0.0002,0.0083,0.0001</t>
+  </si>
+  <si>
+    <t>0.3863,0.2098,0.0608,0.0032</t>
+  </si>
+  <si>
+    <t>0.6620,0.0281,0.1527,0.0023</t>
+  </si>
+  <si>
+    <t>0.0027,0.0066,0.0139,0.9887</t>
+  </si>
+  <si>
+    <t>0.0002,0.9990,0.0104,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0050</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.9025,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.3509,0.6977,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.3251,0.6924,0.0048,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.3311,0.9939,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.8146,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0064,0.0054,0.9853,0.0004</t>
+  </si>
+  <si>
+    <t>0.0005,0.0006,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.9541,0.0022,0.0214,0.0012</t>
+  </si>
+  <si>
+    <t>0.2044,0.0012,0.8353,0.0005</t>
+  </si>
+  <si>
+    <t>0.0148,0.0002,0.9883,0.0004</t>
+  </si>
+  <si>
+    <t>0.9812,0.0007,0.0120,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.0001,0.0000,0.9991</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9977,0.2390,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9501,0.9892,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9491,0.9465,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.7059,0.9817,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9918,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.9902,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.0000,0.0012,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.6389,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0065,0.9903,0.0004,0.0030</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.2515,0.8246,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0984,0.0002,0.0007,0.9665</t>
+  </si>
+  <si>
+    <t>0.0003,0.0018,0.9988,0.0025</t>
+  </si>
+  <si>
+    <t>0.9142,0.0001,0.0674,0.0022</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.0425,0.9588,0.0005,0.0013</t>
+  </si>
+  <si>
+    <t>0.9512,0.0252,0.0087,0.0013</t>
+  </si>
+  <si>
+    <t>0.9936,0.0004,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.4433,0.5221,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.9732,0.0148,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0579,0.9290,0.0047,0.0016</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9987,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.9817,0.0012,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0001,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0232,0.9825,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6144,0.0097,0.3125,0.0005</t>
-  </si>
-  <si>
-    <t>0.9834,0.0006,0.0102,0.0001</t>
-  </si>
-  <si>
-    <t>0.7345,0.0440,0.0432,0.0058</t>
-  </si>
-  <si>
-    <t>0.4696,0.0175,0.3396,0.0036</t>
-  </si>
-  <si>
-    <t>0.0078,0.0109,0.0046,0.9902</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0022</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9385,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7589,0.2588,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.6526,0.4224,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0001,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0008,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9811,0.9962,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.3880,0.9744,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.9851,0.0005,0.0054,0.0001</t>
-  </si>
-  <si>
-    <t>0.5653,0.0012,0.4233,0.0014</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9988,0.0002</t>
-  </si>
-  <si>
-    <t>0.6599,0.0006,0.3982,0.0004</t>
-  </si>
-  <si>
-    <t>0.0478,0.0001,0.0000,0.9860</t>
-  </si>
-  <si>
-    <t>0.0000,0.0203,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.8353,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1124,0.9041,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.4477,0.6307,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9983,0.0006,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0201,0.0004,0.0011,0.9911</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9976,0.0099</t>
-  </si>
-  <si>
-    <t>0.9816,0.0003,0.0084,0.0026</t>
-  </si>
-  <si>
-    <t>0.9957,0.0008,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.0013,0.9963,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9870,0.0047,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.2211,0.6061,0.0196,0.0020</t>
-  </si>
-  <si>
-    <t>0.5231,0.0164,0.3183,0.0002</t>
-  </si>
-  <si>
-    <t>0.8558,0.0285,0.0466,0.0005</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0004,0.0003</t>
+    <t>0.9991,0.0002,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0000,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9963,0.0014,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9941,0.0045,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.2000,0.8394,0.0021,0.0003</t>
-  </si>
-  <si>
-    <t>0.7853,0.2783,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8552,0.0139,0.1308,0.0012</t>
-  </si>
-  <si>
-    <t>0.9977,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0030,0.0005,0.0005</t>
-  </si>
-  <si>
-    <t>0.9912,0.0088,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.9869,0.0071,0.0029,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.0194,0.9910,0.0008</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0023,0.9978,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.0047,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9997,0.0038</t>
-  </si>
-  <si>
-    <t>0.0204,0.0017,0.9814,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.0241,0.0097,0.9199,0.0037</t>
-  </si>
-  <si>
-    <t>0.0051,0.0011,0.9924,0.0002</t>
-  </si>
-  <si>
-    <t>0.0187,0.0413,0.9311,0.0008</t>
-  </si>
-  <si>
-    <t>0.0370,0.0020,0.9616,0.0002</t>
-  </si>
-  <si>
-    <t>0.9225,0.0014,0.0422,0.0051</t>
-  </si>
-  <si>
-    <t>0.0210,0.0019,0.9754,0.0008</t>
-  </si>
-  <si>
-    <t>0.0741,0.9406,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.9979,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0923,0.9280,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9252,0.1129,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.3850,0.7017,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9946,0.0014,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9865,0.0003,0.0092,0.0001</t>
-  </si>
-  <si>
-    <t>0.9638,0.0032,0.0118,0.0015</t>
-  </si>
-  <si>
-    <t>0.0208,0.0101,0.9646,0.0020</t>
-  </si>
-  <si>
-    <t>0.0560,0.0019,0.9426,0.0028</t>
-  </si>
-  <si>
-    <t>0.0140,0.0009,0.9818,0.0047</t>
-  </si>
-  <si>
-    <t>0.0013,0.0038,0.9930,0.0024</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0012,0.9954,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.0029,0.9977,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0028,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.8220,0.3109,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0009,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9969,0.0011,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0458,0.1236,0.6876,0.0012</t>
-  </si>
-  <si>
-    <t>0.7666,0.0009,0.2688,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9997,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.0563,0.9999,0.0000</t>
+    <t>0.9983,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.6307,0.3544,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.1943,0.8465,0.0029,0.0002</t>
+  </si>
+  <si>
+    <t>0.6086,0.4410,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0028,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0038,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9785,0.0234,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9985,0.0005,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9959,0.0023,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.9911,0.0040,0.0021,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0045,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0026,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9994,0.0021</t>
+  </si>
+  <si>
+    <t>0.0051,0.0021,0.9849,0.0053</t>
+  </si>
+  <si>
+    <t>0.0031,0.0002,0.9967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0214,0.0117,0.9204,0.0061</t>
+  </si>
+  <si>
+    <t>0.0112,0.0010,0.9858,0.0004</t>
+  </si>
+  <si>
+    <t>0.0061,0.7761,0.2643,0.0014</t>
+  </si>
+  <si>
+    <t>0.0925,0.0071,0.8881,0.0002</t>
+  </si>
+  <si>
+    <t>0.6881,0.0009,0.2369,0.0053</t>
+  </si>
+  <si>
+    <t>0.0101,0.0005,0.9906,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.9959,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9976,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0429,0.9719,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9785,0.0340,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0754,0.9389,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9939,0.0014,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0000,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9821,0.0018,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.3426,0.0125,0.5528,0.0013</t>
+  </si>
+  <si>
+    <t>0.0565,0.0024,0.9235,0.0077</t>
+  </si>
+  <si>
+    <t>0.0016,0.0007,0.9963,0.0098</t>
+  </si>
+  <si>
+    <t>0.0003,0.0296,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0428,0.9889,0.0011</t>
+  </si>
+  <si>
+    <t>0.0031,0.0009,0.9916,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.0014,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0046,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9989,0.0005</t>
+  </si>
+  <si>
+    <t>0.0650,0.0161,0.8962,0.0016</t>
+  </si>
+  <si>
+    <t>0.6451,0.0017,0.3489,0.0121</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9995,0.0016</t>
+  </si>
+  <si>
+    <t>0.0001,0.0619,0.9989,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0003,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0030,0.9956,0.0002</t>
-  </si>
-  <si>
-    <t>0.0028,0.0022,0.9931,0.0007</t>
-  </si>
-  <si>
-    <t>0.9336,0.0047,0.0284,0.0014</t>
-  </si>
-  <si>
-    <t>0.0827,0.0001,0.9249,0.0010</t>
-  </si>
-  <si>
-    <t>0.9935,0.0001,0.0052,0.0001</t>
+    <t>0.0000,0.0004,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0015,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0011,0.9987,0.0003</t>
+  </si>
+  <si>
+    <t>0.3753,0.0006,0.5233,0.0056</t>
+  </si>
+  <si>
+    <t>0.0032,0.0002,0.9949,0.0009</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0011,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0018,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0574,0.0021,0.9260,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0026,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.0054,0.9920,0.0030</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0109,0.0017,0.9831,0.0013</t>
-  </si>
-  <si>
-    <t>0.3087,0.0055,0.5233,0.0054</t>
-  </si>
-  <si>
-    <t>0.0041,0.0006,0.9902,0.0024</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0020,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.0004,0.0002,0.9992</t>
-  </si>
-  <si>
-    <t>0.6903,0.0005,0.0068,0.2019</t>
+    <t>0.0208,0.0047,0.9601,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0310,0.9908,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.0021,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.0001,0.9975,0.0001</t>
+  </si>
+  <si>
+    <t>0.0015,0.0003,0.9967,0.0018</t>
+  </si>
+  <si>
+    <t>0.0106,0.0059,0.9663,0.0103</t>
+  </si>
+  <si>
+    <t>0.0012,0.0001,0.9975,0.0009</t>
+  </si>
+  <si>
+    <t>0.9804,0.0002,0.0007,0.0120</t>
+  </si>
+  <si>
+    <t>0.0007,0.0065,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0027,0.0001,0.0001,0.9991</t>
+  </si>
+  <si>
+    <t>0.9351,0.0017,0.0013,0.0131</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1902,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1883,7 +1916,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1897,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,10 +1941,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1925,7 +1958,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1939,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1953,7 +1986,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1967,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1981,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1995,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2009,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2023,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2037,7 +2070,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,10 +2081,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2065,7 +2098,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2079,7 +2112,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2093,7 +2126,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2107,7 +2140,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2121,7 +2154,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2135,7 +2168,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2149,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2174,10 +2207,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2191,7 +2224,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2205,7 +2238,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2219,7 +2252,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2233,7 +2266,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2247,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2261,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2275,7 +2308,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2286,10 +2319,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2303,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,10 +2347,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2331,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2345,7 +2378,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2359,7 +2392,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2373,7 +2406,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2387,7 +2420,7 @@
         <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2401,7 +2434,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2415,7 +2448,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2429,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2443,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2457,7 +2490,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2471,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2482,10 +2515,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2499,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2513,7 +2546,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2527,7 +2560,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2541,7 +2574,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2555,7 +2588,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2569,7 +2602,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2583,7 +2616,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2597,7 +2630,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2611,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2625,7 +2658,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2639,7 +2672,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2653,7 +2686,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2667,7 +2700,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2681,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2695,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2709,7 +2742,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2723,7 +2756,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2737,7 +2770,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2751,7 +2784,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2765,7 +2798,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2779,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2793,7 +2826,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2807,7 +2840,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2821,7 +2854,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2835,7 +2868,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2849,7 +2882,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2863,7 +2896,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2877,7 +2910,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2891,7 +2924,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2905,7 +2938,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2919,7 +2952,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2933,7 +2966,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2947,7 +2980,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2961,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2975,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2989,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,10 +3033,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3017,7 +3050,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3031,7 +3064,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,10 +3075,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3059,7 +3092,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3070,10 +3103,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3087,7 +3120,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3101,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3115,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3129,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3143,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3157,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3171,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3185,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3199,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3213,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3227,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3241,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3255,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3269,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3283,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>273</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3297,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3311,7 +3344,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3325,7 +3358,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3339,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3353,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3367,7 +3400,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3381,7 +3414,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3395,7 +3428,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3409,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3423,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>279</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3451,7 +3484,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3465,7 +3498,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3479,7 +3512,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,10 +3523,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3507,7 +3540,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3521,7 +3554,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3535,7 +3568,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3549,7 +3582,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>283</v>
+        <v>377</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3563,7 +3596,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3577,7 +3610,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3591,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3602,10 +3635,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,10 +3649,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3633,7 +3666,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3647,7 +3680,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3661,7 +3694,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>376</v>
+        <v>273</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3675,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3689,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3703,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3717,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3731,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,10 +3775,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3756,10 +3789,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3773,7 +3806,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3787,7 +3820,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3801,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3812,10 +3845,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3829,7 +3862,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3843,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3857,7 +3890,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3871,7 +3904,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>340</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3885,7 +3918,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3899,7 +3932,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3913,7 +3946,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3927,7 +3960,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3941,7 +3974,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3955,7 +3988,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3969,7 +4002,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3983,7 +4016,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3997,7 +4030,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4011,7 +4044,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4025,7 +4058,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4039,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4053,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4067,7 +4100,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4081,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4095,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,7 +4142,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4123,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4134,10 +4167,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4151,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4165,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4179,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4193,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4207,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>375</v>
+        <v>421</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4221,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4249,7 +4282,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>271</v>
+        <v>423</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4263,7 +4296,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,7 +4310,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4291,7 +4324,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4305,7 +4338,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4319,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4333,7 +4366,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4347,7 +4380,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4361,7 +4394,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4375,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4389,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4403,7 +4436,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4417,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4431,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4445,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4459,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4473,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4487,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4501,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4515,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4529,7 +4562,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4543,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,10 +4587,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,7 +4604,7 @@
         <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4585,7 +4618,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4599,7 +4632,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4613,7 +4646,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4627,7 +4660,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4641,7 +4674,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4655,7 +4688,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4669,7 +4702,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4683,7 +4716,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4697,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4711,7 +4744,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4725,7 +4758,7 @@
         <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4739,7 +4772,7 @@
         <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4753,7 +4786,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4767,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4781,7 +4814,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4795,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4809,7 +4842,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4823,7 +4856,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4837,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>402</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4851,7 +4884,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4865,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4879,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4893,7 +4926,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4907,7 +4940,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4921,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>418</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4935,7 +4968,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4949,7 +4982,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4963,7 +4996,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4977,7 +5010,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4991,7 +5024,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5005,7 +5038,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5019,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5033,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5047,7 +5080,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5061,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5075,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,10 +5119,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5103,7 +5136,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5117,7 +5150,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5131,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5145,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5159,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5173,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5187,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>273</v>
+        <v>487</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5201,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5215,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5229,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>270</v>
+        <v>360</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5243,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5257,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>423</v>
+        <v>476</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5271,7 +5304,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5285,7 +5318,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5299,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5313,7 +5346,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5327,7 +5360,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5341,7 +5374,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5355,7 +5388,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5369,7 +5402,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5383,7 +5416,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5397,7 +5430,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>340</v>
+        <v>398</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5411,7 +5444,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>337</v>
+        <v>398</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5425,7 +5458,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
